--- a/data/export/2026-10-18-operations.xlsx
+++ b/data/export/2026-10-18-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,7 +2394,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2363,22 +2407,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2416,7 +2460,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2510,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2523,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2571,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2590,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2626,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2595,22 +2639,22 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2687,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2706,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2742,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2808,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2822,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2858,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2880,7 +2924,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2938,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2974,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3035,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3054,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3090,2915 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-operations.xlsx
+++ b/data/export/2026-10-18-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD47"/>
+  <dimension ref="A1:AD60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1161,12 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,7 +1215,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1544,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1559,7 +1583,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1636,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1675,7 +1699,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1752,7 +1776,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1868,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1922,7 +1946,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2012,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2108,7 +2132,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2162,7 +2186,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2252,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2368,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,41 +2412,45 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2455,12 +2483,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2474,7 +2502,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2499,46 +2527,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2571,12 +2603,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2590,7 +2622,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2615,46 +2647,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2687,12 +2723,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2706,7 +2742,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2731,46 +2767,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2803,12 +2843,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2822,7 +2862,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2847,7 +2887,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2858,35 +2898,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2919,12 +2959,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2938,7 +2978,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2963,7 +3003,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2974,7 +3014,7 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2987,7 +3027,7 @@
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2997,7 +3037,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3035,12 +3075,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3054,7 +3094,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3090,7 +3130,7 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3143,7 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3113,7 +3153,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3123,32 +3163,36 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3156,7 +3200,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3170,7 +3214,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3180,17 +3224,17 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3200,13 +3244,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3267,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3229,7 +3277,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3267,12 +3315,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3286,7 +3334,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3322,7 +3370,7 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3335,22 +3383,22 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3383,12 +3431,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3402,7 +3450,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3438,7 +3486,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3451,22 +3499,22 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3499,12 +3547,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3518,7 +3566,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3554,7 +3602,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3567,22 +3615,22 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3615,12 +3663,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3634,7 +3682,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3670,7 +3718,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3731,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3693,7 +3741,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3731,12 +3779,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3750,7 +3798,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3786,7 +3834,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3847,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3809,7 +3857,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3847,12 +3895,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3866,7 +3914,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3902,7 +3950,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3963,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3925,7 +3973,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3963,12 +4011,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3982,7 +4030,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4018,7 +4066,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4031,22 +4079,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4079,12 +4127,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4098,7 +4146,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4134,7 +4182,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4147,22 +4195,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4195,12 +4243,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4214,7 +4262,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4250,7 +4298,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4311,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4273,7 +4321,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4311,12 +4359,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4330,7 +4378,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4366,7 +4414,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4427,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4427,12 +4475,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4446,7 +4494,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4482,7 +4530,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4495,22 +4543,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4543,12 +4591,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4562,7 +4610,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4598,7 +4646,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4611,22 +4659,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4659,12 +4707,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4678,7 +4726,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4714,35 +4762,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4775,12 +4823,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4794,7 +4842,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4819,7 +4867,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4830,35 +4878,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4891,12 +4939,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4910,7 +4958,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4935,7 +4983,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4946,35 +4994,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5007,12 +5055,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5026,7 +5074,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5062,77 +5110,73 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5146,7 +5190,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5156,17 +5200,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5176,45 +5220,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5247,12 +5287,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5266,7 +5306,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5302,35 +5342,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5363,12 +5403,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5382,7 +5422,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5418,35 +5458,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5479,12 +5519,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5498,7 +5538,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5534,35 +5574,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5600,7 +5640,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5614,7 +5654,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5639,7 +5679,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5650,35 +5690,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5711,12 +5751,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5730,7 +5770,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5766,35 +5806,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5827,12 +5867,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5846,7 +5886,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5882,7 +5922,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5935,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5905,7 +5945,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5915,40 +5955,44 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5962,43 +6006,1579 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>66分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>2/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W47" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X47" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AA57" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr">
+      <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC47" s="2" t="inlineStr"/>
-      <c r="AD47" s="2" t="inlineStr">
-        <is>
-          <t>—/9</t>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/10</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-operations.xlsx
+++ b/data/export/2026-10-18-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD60"/>
+  <dimension ref="A1:AD72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1409,12 +1409,12 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1511,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1544,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1568,17 +1572,17 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1588,13 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1627,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1660,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1684,17 +1696,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1704,13 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1743,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1776,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1800,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1892,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1916,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1936,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2051,7 +2079,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2132,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2171,7 +2199,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2252,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2368,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2488,7 +2516,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2608,7 +2636,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2728,7 +2756,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2848,7 +2876,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2892,13 +2920,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2911,22 +2943,22 @@
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2959,12 +2991,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2978,7 +3010,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3008,41 +3040,45 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3075,12 +3111,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3094,7 +3130,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3119,88 +3155,88 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>115分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3214,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3224,65 +3260,65 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3315,12 +3351,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3334,7 +3370,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3359,18 +3395,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3423,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3393,7 +3433,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3403,32 +3443,36 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3436,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3450,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3460,33 +3504,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3547,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3509,7 +3557,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3519,32 +3567,36 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3552,7 +3604,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3566,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3576,33 +3628,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3671,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3625,7 +3681,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3635,40 +3691,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3682,7 +3742,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3692,17 +3752,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3712,13 +3772,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3731,22 +3795,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3784,7 +3848,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3798,7 +3862,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3834,7 +3898,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3847,60 +3911,64 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3914,7 +3982,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3924,33 +3992,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3963,22 +4035,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4016,7 +4088,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4030,7 +4102,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4066,7 +4138,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4079,22 +4151,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4127,12 +4199,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4146,7 +4218,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4182,7 +4254,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4195,22 +4267,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4243,12 +4315,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4262,7 +4334,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4298,7 +4370,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4383,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4321,7 +4393,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4359,12 +4431,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4378,7 +4450,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4414,7 +4486,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4499,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4437,7 +4509,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4475,12 +4547,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4494,7 +4566,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4530,7 +4602,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4615,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4553,7 +4625,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4591,12 +4663,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4610,7 +4682,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4646,7 +4718,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4731,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4669,7 +4741,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4707,12 +4779,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4726,7 +4798,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4762,7 +4834,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4847,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4785,7 +4857,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4823,12 +4895,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4842,7 +4914,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4878,7 +4950,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4963,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4901,7 +4973,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4939,12 +5011,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4958,7 +5030,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4994,7 +5066,7 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5079,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5017,7 +5089,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5055,12 +5127,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5074,7 +5146,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5110,7 +5182,7 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5195,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5133,7 +5205,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5171,12 +5243,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5190,7 +5262,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5226,7 +5298,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5311,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5249,7 +5321,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5287,12 +5359,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5306,7 +5378,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5342,7 +5414,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5355,22 +5427,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5408,7 +5480,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5422,7 +5494,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5458,7 +5530,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5471,22 +5543,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5519,12 +5591,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5538,7 +5610,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5574,7 +5646,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5587,22 +5659,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5635,12 +5707,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5654,7 +5726,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5690,7 +5762,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5703,22 +5775,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5751,12 +5823,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5770,7 +5842,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5806,7 +5878,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5819,22 +5891,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5872,7 +5944,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5886,7 +5958,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5922,69 +5994,65 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5992,7 +6060,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6006,7 +6074,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6016,65 +6084,61 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6107,12 +6171,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6126,7 +6190,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6151,7 +6215,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6162,35 +6226,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6228,7 +6292,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6242,7 +6306,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6267,7 +6331,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6278,77 +6342,73 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6362,7 +6422,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6372,99 +6432,91 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6472,7 +6524,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6486,7 +6538,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6496,65 +6548,65 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6592,7 +6644,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6606,7 +6658,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6631,46 +6683,50 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6703,12 +6759,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6722,7 +6778,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6758,35 +6814,35 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6824,7 +6880,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6838,7 +6894,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6873,12 +6929,12 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6947,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6901,7 +6957,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6911,40 +6967,44 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6958,7 +7018,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6968,33 +7028,37 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7071,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7017,7 +7081,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7027,40 +7091,44 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7074,7 +7142,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7084,33 +7152,37 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7195,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7133,7 +7205,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7171,12 +7243,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7190,7 +7262,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7226,7 +7298,7 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7311,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7249,7 +7321,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7259,40 +7331,44 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7306,7 +7382,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7316,17 +7392,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7336,13 +7412,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -7355,22 +7435,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7403,12 +7483,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7422,7 +7502,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7447,7 +7527,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7458,7 +7538,7 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/10</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -7471,22 +7551,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7519,12 +7599,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7538,7 +7618,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7568,17 +7648,1425 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AD60" s="2" t="inlineStr">
-        <is>
-          <t>3/10</t>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-operations.xlsx
+++ b/data/export/2026-10-18-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD72"/>
+  <dimension ref="A1:AD97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1769,19 +1769,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2007,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2084,12 +2088,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2127,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2160,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,12 +2212,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2247,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2280,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2304,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2363,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2396,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2420,32 +2440,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2483,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2516,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2540,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2636,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2660,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2723,32 +2751,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2756,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2780,32 +2812,32 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -2843,32 +2875,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2876,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2900,17 +2936,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2920,17 +2956,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2996,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3035,7 +3071,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3045,7 +3081,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3116,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3155,7 +3191,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3170,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3280,12 +3316,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3303,22 +3339,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,12 +3387,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3370,7 +3406,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3395,7 +3431,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3410,77 +3446,73 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3494,7 +3526,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3504,107 +3536,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3618,7 +3646,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3628,107 +3656,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3742,7 +3766,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3752,65 +3776,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3843,12 +3867,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3862,7 +3886,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3887,88 +3911,88 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3982,7 +4006,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3992,65 +4016,65 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4083,12 +4107,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4102,7 +4126,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4127,46 +4151,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4199,12 +4227,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4218,7 +4246,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4243,18 +4271,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4299,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4277,7 +4309,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4287,40 +4319,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4334,7 +4370,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4344,33 +4380,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4423,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4393,7 +4433,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4403,40 +4443,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4450,7 +4494,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4460,33 +4504,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4547,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4509,7 +4557,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4519,40 +4567,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4566,7 +4618,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4576,33 +4628,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4615,60 +4671,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4682,7 +4742,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4692,33 +4752,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4795,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4741,7 +4805,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4751,40 +4815,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4798,7 +4866,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4808,33 +4876,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4919,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4857,7 +4929,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4867,40 +4939,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4914,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4924,33 +5000,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4963,7 +5043,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4973,7 +5053,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4983,40 +5063,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5030,7 +5114,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5040,33 +5124,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5079,60 +5167,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5146,7 +5238,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5156,33 +5248,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5195,60 +5291,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5262,7 +5362,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5272,33 +5372,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5311,60 +5415,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5378,7 +5486,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5388,17 +5496,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5408,13 +5516,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5539,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5437,7 +5549,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5447,40 +5559,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5494,7 +5610,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5504,33 +5620,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5543,32 +5663,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:44</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5591,12 +5711,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5604,13 +5724,21 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
       <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5646,7 +5774,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5659,22 +5787,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5707,12 +5835,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5726,7 +5854,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5762,7 +5890,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5775,60 +5903,64 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5842,7 +5974,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5852,33 +5984,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5891,7 +6027,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5901,7 +6037,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5911,12 +6047,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5939,12 +6075,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5952,13 +6088,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5994,7 +6146,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6159,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6017,7 +6169,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6055,12 +6207,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6074,7 +6226,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6110,7 +6262,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6275,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6133,7 +6285,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6171,12 +6323,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6190,7 +6342,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6226,7 +6378,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6391,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6249,7 +6401,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6287,12 +6439,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6306,7 +6458,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6342,7 +6494,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6507,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6365,7 +6517,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6403,12 +6555,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6422,7 +6574,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6458,7 +6610,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6623,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6481,7 +6633,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6519,12 +6671,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6538,7 +6690,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6563,22 +6715,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6739,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6601,7 +6749,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6639,12 +6787,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6658,7 +6806,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6683,22 +6831,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6855,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6721,7 +6865,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6759,12 +6903,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6778,7 +6922,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6814,7 +6958,7 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6971,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6837,7 +6981,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6880,7 +7024,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6894,7 +7038,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6919,92 +7063,84 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7018,7 +7154,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7028,107 +7164,99 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7142,7 +7270,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7152,65 +7280,61 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7248,7 +7372,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7262,7 +7386,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7287,7 +7411,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7298,77 +7422,73 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7382,7 +7502,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7392,17 +7512,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7417,40 +7537,40 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7488,7 +7608,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7502,7 +7622,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7532,41 +7652,45 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7599,12 +7723,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7618,7 +7742,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7643,7 +7767,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7654,77 +7778,73 @@
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7738,7 +7858,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7748,65 +7868,65 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7844,7 +7964,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7858,7 +7978,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7893,40 +8013,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7959,12 +8079,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7978,7 +8098,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8003,46 +8123,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8075,12 +8199,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8094,7 +8218,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8119,46 +8243,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8191,12 +8319,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8210,7 +8338,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8245,40 +8373,40 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8311,12 +8439,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8330,7 +8458,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8360,41 +8488,45 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8427,12 +8559,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8446,7 +8578,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8482,35 +8614,35 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8543,12 +8675,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8562,7 +8694,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8597,40 +8729,40 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8663,12 +8795,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8682,7 +8814,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8707,46 +8839,50 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8779,12 +8915,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8798,7 +8934,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8828,13 +8964,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -8847,60 +8987,64 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8914,7 +9058,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8924,33 +9068,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8963,60 +9111,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9030,43 +9182,3023 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr"/>
-      <c r="AD72" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-operations.xlsx
+++ b/data/export/2026-10-18-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD47" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7780,12 +7780,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9693,19 +9693,19 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9817,19 +9817,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9931,32 +9931,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9964,7 +9968,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9988,17 +9992,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10008,12 +10012,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10051,32 +10055,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10084,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10108,17 +10116,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10128,12 +10136,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10171,32 +10179,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10204,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10228,17 +10240,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10248,12 +10260,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10324,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10373,7 +10385,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10444,7 +10456,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10488,12 +10500,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10816,7 +10828,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10860,17 +10872,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -10994,7 +11006,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11130,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11200,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11366,7 +11378,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11502,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -11614,7 +11626,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11696,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11808,7 +11820,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11852,17 +11864,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11990,7 +12002,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12122,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12192,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12224,17 +12236,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12312,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12440,7 +12452,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12564,7 +12576,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12608,17 +12620,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12700,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -13056,7 +13068,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13105,12 +13117,12 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13192,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13229,12 +13241,12 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13440,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13552,7 +13564,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -14044,7 +14056,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14098,7 +14110,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14180,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14212,17 +14224,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14482,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -14590,7 +14602,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14672,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14838,7 +14850,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -15094,7 +15106,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -15160,7 +15172,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15204,17 +15216,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15296,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15408,7 +15420,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15452,17 +15464,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -15586,7 +15598,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15668,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15700,17 +15712,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15792,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15904,7 +15916,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16272,7 +16284,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16321,12 +16333,12 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -16396,7 +16408,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16822,7 +16834,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -16888,7 +16900,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16942,7 +16954,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -17066,7 +17078,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -17190,7 +17202,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -17446,7 +17458,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17582,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -17694,7 +17706,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17776,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -18012,7 +18024,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18056,17 +18068,17 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18148,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18185,12 +18197,12 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18698,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18946,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19070,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -19310,7 +19322,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -19380,7 +19392,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19424,17 +19436,17 @@
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -19504,7 +19516,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19628,7 +19640,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19752,7 +19764,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19796,17 +19808,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19888,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19920,17 +19932,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20012,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20124,7 +20136,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20248,7 +20260,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20372,7 +20384,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20496,7 +20508,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20550,7 +20562,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20686,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -20918,7 +20930,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20996,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21282,7 +21294,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -21526,7 +21538,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -21646,7 +21658,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -21821,24 +21833,24 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
@@ -21848,7 +21860,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21897,12 +21909,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -21945,24 +21957,24 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
@@ -21972,7 +21984,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22021,12 +22033,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -22081,12 +22093,12 @@
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O175" s="2" t="inlineStr">
@@ -22096,7 +22108,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22183,32 +22195,36 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N176" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22216,7 +22232,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22240,17 +22256,17 @@
       </c>
       <c r="X176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z176" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA176" s="2" t="inlineStr">
@@ -22260,17 +22276,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -22336,7 +22352,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22423,32 +22439,36 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22456,7 +22476,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22480,17 +22500,17 @@
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA178" s="2" t="inlineStr">
@@ -22500,17 +22520,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -22543,32 +22563,36 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N179" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -22576,7 +22600,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22600,17 +22624,17 @@
       </c>
       <c r="X179" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA179" s="2" t="inlineStr">
@@ -22620,17 +22644,17 @@
       </c>
       <c r="AB179" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -22663,12 +22687,12 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -22696,7 +22720,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22704,10 +22728,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R180" s="2" t="inlineStr"/>
-      <c r="S180" s="2" t="inlineStr"/>
-      <c r="T180" s="2" t="inlineStr"/>
-      <c r="U180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V180" s="2" t="inlineStr">
         <is>
           <t>19:20</t>
@@ -22750,7 +22790,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -22816,7 +22856,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22936,7 +22976,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23023,32 +23063,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23056,7 +23100,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23080,17 +23124,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23100,17 +23144,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -23176,7 +23220,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23296,7 +23340,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23416,7 +23460,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23536,7 +23580,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23585,12 +23629,12 @@
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23758,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -23838,7 +23882,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -24450,7 +24494,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -24574,7 +24618,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24684,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24764,7 +24808,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24813,12 +24857,12 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -24942,7 +24986,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -25132,7 +25176,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25176,12 +25220,12 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
@@ -25426,7 +25470,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -25620,7 +25664,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25664,17 +25708,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -25864,7 +25908,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25908,12 +25952,12 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
@@ -25988,7 +26032,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26032,12 +26076,12 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26162,7 +26206,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -26232,7 +26276,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26406,7 +26450,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -26530,7 +26574,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26640,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26645,12 +26689,12 @@
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -27018,7 +27062,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -27088,7 +27132,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27132,12 +27176,12 @@
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27332,7 +27376,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27376,17 +27420,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -27456,7 +27500,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27500,12 +27544,12 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
@@ -27634,7 +27678,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -27704,7 +27748,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27748,12 +27792,12 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
@@ -27828,7 +27872,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27877,12 +27921,12 @@
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -28006,7 +28050,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -28200,7 +28244,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28244,12 +28288,12 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
@@ -28374,7 +28418,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -28444,7 +28488,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28488,17 +28532,17 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -28618,7 +28662,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -28688,7 +28732,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28732,12 +28776,12 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
@@ -28812,7 +28856,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28856,12 +28900,12 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -28990,7 +29034,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29100,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29100,17 +29144,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -29234,7 +29278,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -29478,7 +29522,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -29672,7 +29716,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29716,12 +29760,12 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
@@ -29792,7 +29836,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29916,7 +29960,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29960,17 +30004,17 @@
       </c>
       <c r="AB239" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -30040,7 +30084,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30089,12 +30133,12 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -30218,7 +30262,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -30466,7 +30510,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -30536,7 +30580,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30580,12 +30624,12 @@
       </c>
       <c r="AB244" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC244" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD244" s="2" t="inlineStr">
@@ -30784,7 +30828,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30828,17 +30872,17 @@
       </c>
       <c r="AB246" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -30908,7 +30952,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31086,7 +31130,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31324,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31329,12 +31373,12 @@
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -31400,7 +31444,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31444,12 +31488,12 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
@@ -31524,7 +31568,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31568,12 +31612,12 @@
       </c>
       <c r="AB252" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
@@ -31702,7 +31746,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -31772,7 +31816,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31816,17 +31860,17 @@
       </c>
       <c r="AB254" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC254" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31950,7 +31994,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -32194,7 +32238,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -32264,7 +32308,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32308,12 +32352,12 @@
       </c>
       <c r="AB258" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
@@ -32512,7 +32556,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32556,17 +32600,17 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32858,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33004,7 +33048,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33128,7 +33172,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33172,12 +33216,12 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
@@ -33252,7 +33296,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33296,12 +33340,12 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33376,7 +33420,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33425,12 +33469,12 @@
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -33500,7 +33544,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33544,17 +33588,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33678,7 +33722,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -33922,7 +33966,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -34046,7 +34090,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -34116,7 +34160,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34160,12 +34204,12 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
@@ -34360,7 +34404,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34404,17 +34448,17 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -34662,7 +34706,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -34732,7 +34776,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34939,32 +34983,36 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr"/>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N280" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O280" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34972,7 +35020,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -34996,17 +35044,17 @@
       </c>
       <c r="X280" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z280" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA280" s="2" t="inlineStr">
@@ -35016,12 +35064,12 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
@@ -35266,7 +35314,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -35309,24 +35357,24 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N283" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O283" s="2" t="inlineStr">
@@ -35336,7 +35384,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35385,12 +35433,12 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -35423,32 +35471,36 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N284" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O284" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -35456,7 +35508,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35480,17 +35532,17 @@
       </c>
       <c r="X284" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA284" s="2" t="inlineStr">
@@ -35500,12 +35552,12 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35543,32 +35595,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -35576,7 +35632,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35600,17 +35656,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35620,17 +35676,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -35663,32 +35719,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35696,7 +35756,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35720,17 +35780,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35740,12 +35800,12 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -35783,32 +35843,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35816,7 +35880,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35840,17 +35904,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35860,17 +35924,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -35936,7 +36000,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35980,12 +36044,12 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36056,7 +36120,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36100,17 +36164,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-operations.xlsx
+++ b/data/export/2026-10-18-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7656,12 +7656,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10303,32 +10303,36 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10336,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10360,17 +10364,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10380,12 +10384,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10423,32 +10427,36 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10456,7 +10464,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10480,17 +10488,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10500,12 +10508,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -11200,7 +11208,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11244,12 +11252,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11502,7 +11510,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11634,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11704,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11740,17 +11748,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12241,12 +12249,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12460,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12630,7 +12638,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12708,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12744,17 +12752,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -13068,7 +13076,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13246,7 +13254,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13626,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13750,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14064,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14672,7 +14680,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14716,12 +14724,12 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
@@ -14850,7 +14858,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15114,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15304,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15340,17 +15348,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15428,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15469,12 +15477,12 @@
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15730,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -15792,7 +15800,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15916,7 +15924,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15960,17 +15968,17 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16292,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16586,7 +16594,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16908,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -17202,7 +17210,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -17458,7 +17466,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -18078,7 +18086,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18210,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -18450,7 +18458,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18954,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -19570,7 +19578,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -19764,7 +19772,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19813,12 +19821,12 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -20012,7 +20020,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20056,17 +20064,17 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20144,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20180,12 +20188,12 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
@@ -20384,7 +20392,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20428,17 +20436,17 @@
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20516,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20930,7 +20938,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -20996,7 +21004,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21860,7 +21868,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -22038,7 +22046,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -22162,7 +22170,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -22286,7 +22294,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22700,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -22720,7 +22728,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22943,32 +22951,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -22976,7 +22988,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23000,17 +23012,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -23020,12 +23032,12 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
@@ -23073,24 +23085,24 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O183" s="2" t="inlineStr">
@@ -23100,7 +23112,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23149,12 +23161,12 @@
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -23187,32 +23199,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23220,7 +23236,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23244,17 +23260,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23264,17 +23280,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -23307,32 +23323,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23340,7 +23360,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23364,17 +23384,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23384,17 +23404,17 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -23460,7 +23480,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23580,7 +23600,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -25664,7 +25684,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25713,7 +25733,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25908,7 +25928,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25952,12 +25972,12 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
@@ -27376,7 +27396,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27425,7 +27445,7 @@
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
@@ -27748,7 +27768,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27792,12 +27812,12 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
@@ -28488,7 +28508,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28537,7 +28557,7 @@
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
@@ -28732,7 +28752,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28776,12 +28796,12 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
@@ -29100,7 +29120,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29960,7 +29980,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -30828,7 +30848,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30877,7 +30897,7 @@
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
@@ -31568,7 +31588,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q252" s="2" t="inlineStr">
@@ -31612,12 +31632,12 @@
       </c>
       <c r="AB252" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC252" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD252" s="2" t="inlineStr">
@@ -31816,7 +31836,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -32556,7 +32576,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32605,7 +32625,7 @@
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -33296,7 +33316,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33340,12 +33360,12 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33544,7 +33564,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -34404,7 +34424,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34453,7 +34473,7 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -35508,7 +35528,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35552,12 +35572,12 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35632,7 +35652,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35853,12 +35873,12 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
@@ -35880,7 +35900,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35929,7 +35949,7 @@
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
@@ -35967,32 +35987,36 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O288" s="2" t="inlineStr">
         <is>
           <t>08:30</t>
@@ -36000,7 +36024,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36024,17 +36048,17 @@
       </c>
       <c r="X288" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA288" s="2" t="inlineStr">
@@ -36044,12 +36068,12 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
@@ -36120,7 +36144,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
